--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3746,6 +3746,1568 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121905252</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>563976</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6703236</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121905270</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91124</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>563981</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6703238</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121905256</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>564058</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6703198</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121905254</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>564000</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6703261</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121905251</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>563979</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6703240</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121905247</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>563953</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6703296</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121905260</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91168</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>563977</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6703232</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121905263</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>564103</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6703266</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121905250</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>563964</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703266</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121905261</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91014</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>563990</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6703247</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121905268</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>564170</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6703165</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121905245</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>563978</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6703314</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121905249</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>563954</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6703267</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121905253</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>563982</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6703249</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121905244</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>563967</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6703314</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,7 +3748,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905252</v>
+        <v>121905244</v>
       </c>
       <c r="B29" t="n">
         <v>90728</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563976</v>
+        <v>563967</v>
       </c>
       <c r="R29" t="n">
-        <v>6703236</v>
+        <v>6703314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905270</v>
+        <v>121905261</v>
       </c>
       <c r="B30" t="n">
-        <v>91124</v>
+        <v>91014</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,25 +3862,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563981</v>
+        <v>563990</v>
       </c>
       <c r="R30" t="n">
-        <v>6703238</v>
+        <v>6703247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,11 +3926,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3957,10 +3952,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905256</v>
+        <v>121905260</v>
       </c>
       <c r="B31" t="n">
-        <v>56569</v>
+        <v>91168</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,46 +3964,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564058</v>
+        <v>563977</v>
       </c>
       <c r="R31" t="n">
-        <v>6703198</v>
+        <v>6703232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4067,7 +4054,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905254</v>
+        <v>121905252</v>
       </c>
       <c r="B32" t="n">
         <v>90728</v>
@@ -4107,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564000</v>
+        <v>563976</v>
       </c>
       <c r="R32" t="n">
-        <v>6703261</v>
+        <v>6703236</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4271,10 +4258,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905247</v>
+        <v>121905256</v>
       </c>
       <c r="B34" t="n">
-        <v>90728</v>
+        <v>56569</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4283,38 +4270,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563953</v>
+        <v>564058</v>
       </c>
       <c r="R34" t="n">
-        <v>6703296</v>
+        <v>6703198</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905260</v>
+        <v>121905249</v>
       </c>
       <c r="B35" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,25 +4380,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4413,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563977</v>
+        <v>563954</v>
       </c>
       <c r="R35" t="n">
-        <v>6703232</v>
+        <v>6703267</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,10 +4470,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905263</v>
+        <v>121905254</v>
       </c>
       <c r="B36" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4487,46 +4482,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564103</v>
+        <v>564000</v>
       </c>
       <c r="R36" t="n">
-        <v>6703266</v>
+        <v>6703261</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,18 +4548,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905250</v>
+        <v>121905263</v>
       </c>
       <c r="B37" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4603,35 +4584,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563964</v>
+        <v>564103</v>
       </c>
       <c r="R37" t="n">
         <v>6703266</v>
@@ -4669,12 +4658,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4693,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905261</v>
+        <v>121905247</v>
       </c>
       <c r="B38" t="n">
-        <v>91014</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4709,21 +4704,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563990</v>
+        <v>563953</v>
       </c>
       <c r="R38" t="n">
-        <v>6703247</v>
+        <v>6703296</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4795,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905268</v>
+        <v>121905250</v>
       </c>
       <c r="B39" t="n">
-        <v>5173</v>
+        <v>90728</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4807,43 +4802,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564170</v>
+        <v>563964</v>
       </c>
       <c r="R39" t="n">
-        <v>6703165</v>
+        <v>6703266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4902,7 +4892,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905245</v>
+        <v>121905253</v>
       </c>
       <c r="B40" t="n">
         <v>90728</v>
@@ -4942,10 +4932,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563978</v>
+        <v>563982</v>
       </c>
       <c r="R40" t="n">
-        <v>6703314</v>
+        <v>6703249</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5004,10 +4994,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905249</v>
+        <v>121905268</v>
       </c>
       <c r="B41" t="n">
-        <v>90728</v>
+        <v>5173</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,38 +5006,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563954</v>
+        <v>564170</v>
       </c>
       <c r="R41" t="n">
-        <v>6703267</v>
+        <v>6703165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5106,10 +5101,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905253</v>
+        <v>121905270</v>
       </c>
       <c r="B42" t="n">
-        <v>90728</v>
+        <v>91124</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5118,25 +5113,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,10 +5141,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563982</v>
+        <v>563981</v>
       </c>
       <c r="R42" t="n">
-        <v>6703249</v>
+        <v>6703238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,6 +5177,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5208,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905244</v>
+        <v>121905245</v>
       </c>
       <c r="B43" t="n">
         <v>90728</v>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563967</v>
+        <v>563978</v>
       </c>
       <c r="R43" t="n">
         <v>6703314</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905244</v>
+        <v>121905268</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,38 +3760,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563967</v>
+        <v>564170</v>
       </c>
       <c r="R29" t="n">
-        <v>6703314</v>
+        <v>6703165</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905261</v>
+        <v>121905270</v>
       </c>
       <c r="B30" t="n">
-        <v>91014</v>
+        <v>91124</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,25 +3867,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>4217</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3890,10 +3895,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563990</v>
+        <v>563981</v>
       </c>
       <c r="R30" t="n">
-        <v>6703247</v>
+        <v>6703238</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,6 +3931,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905260</v>
+        <v>121905244</v>
       </c>
       <c r="B31" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,25 +3974,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3992,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563977</v>
+        <v>563967</v>
       </c>
       <c r="R31" t="n">
-        <v>6703232</v>
+        <v>6703314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4156,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905251</v>
+        <v>121905263</v>
       </c>
       <c r="B33" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,38 +4178,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563979</v>
+        <v>564103</v>
       </c>
       <c r="R33" t="n">
-        <v>6703240</v>
+        <v>6703266</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,12 +4252,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4282,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905256</v>
+        <v>121905253</v>
       </c>
       <c r="B34" t="n">
-        <v>56569</v>
+        <v>90728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4270,46 +4294,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564058</v>
+        <v>563982</v>
       </c>
       <c r="R34" t="n">
-        <v>6703198</v>
+        <v>6703249</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4368,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905249</v>
+        <v>121905260</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4380,25 +4396,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4408,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563954</v>
+        <v>563977</v>
       </c>
       <c r="R35" t="n">
-        <v>6703267</v>
+        <v>6703232</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4470,10 +4486,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905254</v>
+        <v>121905256</v>
       </c>
       <c r="B36" t="n">
-        <v>90728</v>
+        <v>56569</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4482,38 +4498,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564000</v>
+        <v>564058</v>
       </c>
       <c r="R36" t="n">
-        <v>6703261</v>
+        <v>6703198</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4572,10 +4596,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905263</v>
+        <v>121905261</v>
       </c>
       <c r="B37" t="n">
-        <v>98113</v>
+        <v>91014</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4584,46 +4608,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564103</v>
+        <v>563990</v>
       </c>
       <c r="R37" t="n">
-        <v>6703266</v>
+        <v>6703247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4658,18 +4674,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4688,7 +4698,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905247</v>
+        <v>121905254</v>
       </c>
       <c r="B38" t="n">
         <v>90728</v>
@@ -4728,10 +4738,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563953</v>
+        <v>564000</v>
       </c>
       <c r="R38" t="n">
-        <v>6703296</v>
+        <v>6703261</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4892,7 +4902,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905253</v>
+        <v>121905249</v>
       </c>
       <c r="B40" t="n">
         <v>90728</v>
@@ -4932,10 +4942,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563982</v>
+        <v>563954</v>
       </c>
       <c r="R40" t="n">
-        <v>6703249</v>
+        <v>6703267</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4994,10 +5004,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905268</v>
+        <v>121905251</v>
       </c>
       <c r="B41" t="n">
-        <v>5173</v>
+        <v>90728</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5006,43 +5016,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564170</v>
+        <v>563979</v>
       </c>
       <c r="R41" t="n">
-        <v>6703165</v>
+        <v>6703240</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5101,10 +5106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905270</v>
+        <v>121905245</v>
       </c>
       <c r="B42" t="n">
-        <v>91124</v>
+        <v>90728</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5113,25 +5118,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5141,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563981</v>
+        <v>563978</v>
       </c>
       <c r="R42" t="n">
-        <v>6703238</v>
+        <v>6703314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5177,11 +5182,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5208,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905245</v>
+        <v>121905247</v>
       </c>
       <c r="B43" t="n">
         <v>90728</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563978</v>
+        <v>563953</v>
       </c>
       <c r="R43" t="n">
-        <v>6703314</v>
+        <v>6703296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905268</v>
+        <v>121905261</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>91014</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,43 +3760,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564170</v>
+        <v>563990</v>
       </c>
       <c r="R29" t="n">
-        <v>6703165</v>
+        <v>6703247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905270</v>
+        <v>121905247</v>
       </c>
       <c r="B30" t="n">
-        <v>91124</v>
+        <v>90728</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,25 +3862,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3895,10 +3890,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563981</v>
+        <v>563953</v>
       </c>
       <c r="R30" t="n">
-        <v>6703238</v>
+        <v>6703296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,11 +3926,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,7 +3952,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905244</v>
+        <v>121905254</v>
       </c>
       <c r="B31" t="n">
         <v>90728</v>
@@ -4002,10 +3992,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563967</v>
+        <v>564000</v>
       </c>
       <c r="R31" t="n">
-        <v>6703314</v>
+        <v>6703261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4064,7 +4054,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905252</v>
+        <v>121905250</v>
       </c>
       <c r="B32" t="n">
         <v>90728</v>
@@ -4104,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563976</v>
+        <v>563964</v>
       </c>
       <c r="R32" t="n">
-        <v>6703236</v>
+        <v>6703266</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4166,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905263</v>
+        <v>121905270</v>
       </c>
       <c r="B33" t="n">
-        <v>98113</v>
+        <v>91124</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,46 +4168,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564103</v>
+        <v>563981</v>
       </c>
       <c r="R33" t="n">
-        <v>6703266</v>
+        <v>6703238</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,7 +4236,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,7 +4245,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4282,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905253</v>
+        <v>121905256</v>
       </c>
       <c r="B34" t="n">
-        <v>90728</v>
+        <v>56569</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4294,38 +4275,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563982</v>
+        <v>564058</v>
       </c>
       <c r="R34" t="n">
-        <v>6703249</v>
+        <v>6703198</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4384,10 +4373,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905260</v>
+        <v>121905251</v>
       </c>
       <c r="B35" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4396,25 +4385,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4424,10 +4413,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563977</v>
+        <v>563979</v>
       </c>
       <c r="R35" t="n">
-        <v>6703232</v>
+        <v>6703240</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4486,10 +4475,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905256</v>
+        <v>121905260</v>
       </c>
       <c r="B36" t="n">
-        <v>56569</v>
+        <v>91168</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4498,46 +4487,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564058</v>
+        <v>563977</v>
       </c>
       <c r="R36" t="n">
-        <v>6703198</v>
+        <v>6703232</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,10 +4577,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905261</v>
+        <v>121905253</v>
       </c>
       <c r="B37" t="n">
-        <v>91014</v>
+        <v>90728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,21 +4593,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4636,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563990</v>
+        <v>563982</v>
       </c>
       <c r="R37" t="n">
-        <v>6703247</v>
+        <v>6703249</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,7 +4679,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905254</v>
+        <v>121905252</v>
       </c>
       <c r="B38" t="n">
         <v>90728</v>
@@ -4738,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564000</v>
+        <v>563976</v>
       </c>
       <c r="R38" t="n">
-        <v>6703261</v>
+        <v>6703236</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4800,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905250</v>
+        <v>121905263</v>
       </c>
       <c r="B39" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4812,35 +4793,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563964</v>
+        <v>564103</v>
       </c>
       <c r="R39" t="n">
         <v>6703266</v>
@@ -4878,12 +4867,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5004,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905251</v>
+        <v>121905268</v>
       </c>
       <c r="B41" t="n">
-        <v>90728</v>
+        <v>5173</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,38 +5011,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563979</v>
+        <v>564170</v>
       </c>
       <c r="R41" t="n">
-        <v>6703240</v>
+        <v>6703165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905247</v>
+        <v>121905244</v>
       </c>
       <c r="B43" t="n">
         <v>90728</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563953</v>
+        <v>563967</v>
       </c>
       <c r="R43" t="n">
-        <v>6703296</v>
+        <v>6703314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905261</v>
+        <v>121905263</v>
       </c>
       <c r="B29" t="n">
-        <v>91014</v>
+        <v>98131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,38 +3760,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563990</v>
+        <v>564103</v>
       </c>
       <c r="R29" t="n">
-        <v>6703247</v>
+        <v>6703266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3826,12 +3834,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3850,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905247</v>
+        <v>121905253</v>
       </c>
       <c r="B30" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3890,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563953</v>
+        <v>563982</v>
       </c>
       <c r="R30" t="n">
-        <v>6703296</v>
+        <v>6703249</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3952,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905254</v>
+        <v>121905251</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3992,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564000</v>
+        <v>563979</v>
       </c>
       <c r="R31" t="n">
-        <v>6703261</v>
+        <v>6703240</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4054,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905250</v>
+        <v>121905254</v>
       </c>
       <c r="B32" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4094,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563964</v>
+        <v>564000</v>
       </c>
       <c r="R32" t="n">
-        <v>6703266</v>
+        <v>6703261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905270</v>
+        <v>121905245</v>
       </c>
       <c r="B33" t="n">
-        <v>91124</v>
+        <v>90742</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,25 +4182,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4196,10 +4210,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563981</v>
+        <v>563978</v>
       </c>
       <c r="R33" t="n">
-        <v>6703238</v>
+        <v>6703314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,11 +4246,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905256</v>
+        <v>121905250</v>
       </c>
       <c r="B34" t="n">
-        <v>56569</v>
+        <v>90742</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,46 +4284,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564058</v>
+        <v>563964</v>
       </c>
       <c r="R34" t="n">
-        <v>6703198</v>
+        <v>6703266</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905251</v>
+        <v>121905260</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>91182</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,25 +4386,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4413,10 +4414,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563979</v>
+        <v>563977</v>
       </c>
       <c r="R35" t="n">
-        <v>6703240</v>
+        <v>6703232</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905260</v>
+        <v>121905261</v>
       </c>
       <c r="B36" t="n">
-        <v>91168</v>
+        <v>91028</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4487,25 +4488,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4515,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563977</v>
+        <v>563990</v>
       </c>
       <c r="R36" t="n">
-        <v>6703232</v>
+        <v>6703247</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4577,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905253</v>
+        <v>121905247</v>
       </c>
       <c r="B37" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4617,10 +4618,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563982</v>
+        <v>563953</v>
       </c>
       <c r="R37" t="n">
-        <v>6703249</v>
+        <v>6703296</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4679,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905252</v>
+        <v>121905270</v>
       </c>
       <c r="B38" t="n">
-        <v>90728</v>
+        <v>91138</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4691,25 +4692,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4719,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563976</v>
+        <v>563981</v>
       </c>
       <c r="R38" t="n">
-        <v>6703236</v>
+        <v>6703238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4755,6 +4756,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4781,10 +4787,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905263</v>
+        <v>121905252</v>
       </c>
       <c r="B39" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4793,46 +4799,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564103</v>
+        <v>563976</v>
       </c>
       <c r="R39" t="n">
-        <v>6703266</v>
+        <v>6703236</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4867,18 +4865,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905249</v>
+        <v>121905244</v>
       </c>
       <c r="B40" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4937,10 +4929,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563954</v>
+        <v>563967</v>
       </c>
       <c r="R40" t="n">
-        <v>6703267</v>
+        <v>6703314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4999,10 +4991,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905268</v>
+        <v>121905256</v>
       </c>
       <c r="B41" t="n">
-        <v>5173</v>
+        <v>56577</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5015,39 +5007,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564170</v>
+        <v>564058</v>
       </c>
       <c r="R41" t="n">
-        <v>6703165</v>
+        <v>6703198</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5106,10 +5101,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905245</v>
+        <v>121905249</v>
       </c>
       <c r="B42" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5146,10 +5141,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563978</v>
+        <v>563954</v>
       </c>
       <c r="R42" t="n">
-        <v>6703314</v>
+        <v>6703267</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5208,10 +5203,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905244</v>
+        <v>121905268</v>
       </c>
       <c r="B43" t="n">
-        <v>90728</v>
+        <v>5173</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5220,38 +5215,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563967</v>
+        <v>564170</v>
       </c>
       <c r="R43" t="n">
-        <v>6703314</v>
+        <v>6703165</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905263</v>
+        <v>121905245</v>
       </c>
       <c r="B29" t="n">
-        <v>98131</v>
+        <v>90744</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,46 +3760,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564103</v>
+        <v>563978</v>
       </c>
       <c r="R29" t="n">
-        <v>6703266</v>
+        <v>6703314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,18 +3826,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3864,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905253</v>
+        <v>121905270</v>
       </c>
       <c r="B30" t="n">
-        <v>90742</v>
+        <v>91140</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,25 +3862,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3890,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563982</v>
+        <v>563981</v>
       </c>
       <c r="R30" t="n">
-        <v>6703249</v>
+        <v>6703238</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3940,6 +3926,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,10 +3957,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905251</v>
+        <v>121905260</v>
       </c>
       <c r="B31" t="n">
-        <v>90742</v>
+        <v>91184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3978,25 +3969,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4006,10 +3997,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563979</v>
+        <v>563977</v>
       </c>
       <c r="R31" t="n">
-        <v>6703240</v>
+        <v>6703232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4068,10 +4059,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905254</v>
+        <v>121905253</v>
       </c>
       <c r="B32" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564000</v>
+        <v>563982</v>
       </c>
       <c r="R32" t="n">
-        <v>6703261</v>
+        <v>6703249</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4170,10 +4161,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905245</v>
+        <v>121905247</v>
       </c>
       <c r="B33" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,10 +4201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563978</v>
+        <v>563953</v>
       </c>
       <c r="R33" t="n">
-        <v>6703314</v>
+        <v>6703296</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4275,7 +4266,7 @@
         <v>121905250</v>
       </c>
       <c r="B34" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4374,10 +4365,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905260</v>
+        <v>121905249</v>
       </c>
       <c r="B35" t="n">
-        <v>91182</v>
+        <v>90744</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4386,25 +4377,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4414,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563977</v>
+        <v>563954</v>
       </c>
       <c r="R35" t="n">
-        <v>6703232</v>
+        <v>6703267</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4476,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905261</v>
+        <v>121905263</v>
       </c>
       <c r="B36" t="n">
-        <v>91028</v>
+        <v>98133</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4488,38 +4479,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563990</v>
+        <v>564103</v>
       </c>
       <c r="R36" t="n">
-        <v>6703247</v>
+        <v>6703266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4554,12 +4553,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4578,10 +4583,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905247</v>
+        <v>121905261</v>
       </c>
       <c r="B37" t="n">
-        <v>90742</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,21 +4599,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4618,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563953</v>
+        <v>563990</v>
       </c>
       <c r="R37" t="n">
-        <v>6703296</v>
+        <v>6703247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4680,10 +4685,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905270</v>
+        <v>121905244</v>
       </c>
       <c r="B38" t="n">
-        <v>91138</v>
+        <v>90744</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4692,25 +4697,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,10 +4725,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563981</v>
+        <v>563967</v>
       </c>
       <c r="R38" t="n">
-        <v>6703238</v>
+        <v>6703314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4756,11 +4761,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4787,10 +4787,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905252</v>
+        <v>121905254</v>
       </c>
       <c r="B39" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563976</v>
+        <v>564000</v>
       </c>
       <c r="R39" t="n">
-        <v>6703236</v>
+        <v>6703261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905244</v>
+        <v>121905268</v>
       </c>
       <c r="B40" t="n">
-        <v>90742</v>
+        <v>5173</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4901,38 +4901,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563967</v>
+        <v>564170</v>
       </c>
       <c r="R40" t="n">
-        <v>6703314</v>
+        <v>6703165</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4991,10 +4996,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905256</v>
+        <v>121905251</v>
       </c>
       <c r="B41" t="n">
-        <v>56577</v>
+        <v>90744</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5003,46 +5008,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564058</v>
+        <v>563979</v>
       </c>
       <c r="R41" t="n">
-        <v>6703198</v>
+        <v>6703240</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5101,10 +5098,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905249</v>
+        <v>121905252</v>
       </c>
       <c r="B42" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5141,10 +5138,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563954</v>
+        <v>563976</v>
       </c>
       <c r="R42" t="n">
-        <v>6703267</v>
+        <v>6703236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5203,10 +5200,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905268</v>
+        <v>121905256</v>
       </c>
       <c r="B43" t="n">
-        <v>5173</v>
+        <v>56577</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5219,39 +5216,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564170</v>
+        <v>564058</v>
       </c>
       <c r="R43" t="n">
-        <v>6703165</v>
+        <v>6703198</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3751,7 +3751,7 @@
         <v>121905245</v>
       </c>
       <c r="B29" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905270</v>
+        <v>121905247</v>
       </c>
       <c r="B30" t="n">
-        <v>91140</v>
+        <v>90745</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,25 +3862,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563981</v>
+        <v>563953</v>
       </c>
       <c r="R30" t="n">
-        <v>6703238</v>
+        <v>6703296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,11 +3926,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,7 +3955,7 @@
         <v>121905260</v>
       </c>
       <c r="B31" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4059,10 +4054,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905253</v>
+        <v>121905250</v>
       </c>
       <c r="B32" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563982</v>
+        <v>563964</v>
       </c>
       <c r="R32" t="n">
-        <v>6703249</v>
+        <v>6703266</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4161,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905247</v>
+        <v>121905256</v>
       </c>
       <c r="B33" t="n">
-        <v>90744</v>
+        <v>56577</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4173,38 +4168,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563953</v>
+        <v>564058</v>
       </c>
       <c r="R33" t="n">
-        <v>6703296</v>
+        <v>6703198</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4263,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905250</v>
+        <v>121905254</v>
       </c>
       <c r="B34" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,10 +4306,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563964</v>
+        <v>564000</v>
       </c>
       <c r="R34" t="n">
-        <v>6703266</v>
+        <v>6703261</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4365,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905249</v>
+        <v>121905244</v>
       </c>
       <c r="B35" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4405,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563954</v>
+        <v>563967</v>
       </c>
       <c r="R35" t="n">
-        <v>6703267</v>
+        <v>6703314</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,10 +4470,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905263</v>
+        <v>121905249</v>
       </c>
       <c r="B36" t="n">
-        <v>98133</v>
+        <v>90745</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4479,46 +4482,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564103</v>
+        <v>563954</v>
       </c>
       <c r="R36" t="n">
-        <v>6703266</v>
+        <v>6703267</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4553,18 +4548,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4583,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905261</v>
+        <v>121905253</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>90745</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4599,21 +4588,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4623,10 +4612,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563990</v>
+        <v>563982</v>
       </c>
       <c r="R37" t="n">
-        <v>6703247</v>
+        <v>6703249</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4685,10 +4674,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905244</v>
+        <v>121905268</v>
       </c>
       <c r="B38" t="n">
-        <v>90744</v>
+        <v>5173</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4697,38 +4686,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563967</v>
+        <v>564170</v>
       </c>
       <c r="R38" t="n">
-        <v>6703314</v>
+        <v>6703165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4787,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905254</v>
+        <v>121905270</v>
       </c>
       <c r="B39" t="n">
-        <v>90744</v>
+        <v>91141</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4799,25 +4793,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,10 +4821,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564000</v>
+        <v>563981</v>
       </c>
       <c r="R39" t="n">
-        <v>6703261</v>
+        <v>6703238</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4863,6 +4857,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905268</v>
+        <v>121905261</v>
       </c>
       <c r="B40" t="n">
-        <v>5173</v>
+        <v>91031</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4901,43 +4900,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564170</v>
+        <v>563990</v>
       </c>
       <c r="R40" t="n">
-        <v>6703165</v>
+        <v>6703247</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4996,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905251</v>
+        <v>121905252</v>
       </c>
       <c r="B41" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5036,10 +5030,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563979</v>
+        <v>563976</v>
       </c>
       <c r="R41" t="n">
-        <v>6703240</v>
+        <v>6703236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5098,10 +5092,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905252</v>
+        <v>121905251</v>
       </c>
       <c r="B42" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5138,10 +5132,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563976</v>
+        <v>563979</v>
       </c>
       <c r="R42" t="n">
-        <v>6703236</v>
+        <v>6703240</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5200,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905256</v>
+        <v>121905263</v>
       </c>
       <c r="B43" t="n">
-        <v>56577</v>
+        <v>98140</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5212,35 +5206,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5248,10 +5242,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564058</v>
+        <v>564103</v>
       </c>
       <c r="R43" t="n">
-        <v>6703198</v>
+        <v>6703266</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5286,12 +5280,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905245</v>
+        <v>121905263</v>
       </c>
       <c r="B29" t="n">
-        <v>90745</v>
+        <v>98149</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,38 +3760,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563978</v>
+        <v>564103</v>
       </c>
       <c r="R29" t="n">
-        <v>6703314</v>
+        <v>6703266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3826,12 +3834,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3853,7 +3867,7 @@
         <v>121905247</v>
       </c>
       <c r="B30" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905260</v>
+        <v>121905250</v>
       </c>
       <c r="B31" t="n">
-        <v>91185</v>
+        <v>90754</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,25 +3978,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3992,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563977</v>
+        <v>563964</v>
       </c>
       <c r="R31" t="n">
-        <v>6703232</v>
+        <v>6703266</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4054,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905250</v>
+        <v>121905261</v>
       </c>
       <c r="B32" t="n">
-        <v>90745</v>
+        <v>91040</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,21 +4084,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4094,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563964</v>
+        <v>563990</v>
       </c>
       <c r="R32" t="n">
-        <v>6703266</v>
+        <v>6703247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905256</v>
+        <v>121905251</v>
       </c>
       <c r="B33" t="n">
-        <v>56577</v>
+        <v>90754</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,46 +4182,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564058</v>
+        <v>563979</v>
       </c>
       <c r="R33" t="n">
-        <v>6703198</v>
+        <v>6703240</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4266,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905254</v>
+        <v>121905253</v>
       </c>
       <c r="B34" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4306,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564000</v>
+        <v>563982</v>
       </c>
       <c r="R34" t="n">
-        <v>6703261</v>
+        <v>6703249</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4368,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905244</v>
+        <v>121905249</v>
       </c>
       <c r="B35" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4408,10 +4414,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563967</v>
+        <v>563954</v>
       </c>
       <c r="R35" t="n">
-        <v>6703314</v>
+        <v>6703267</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4470,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905249</v>
+        <v>121905256</v>
       </c>
       <c r="B36" t="n">
-        <v>90745</v>
+        <v>56581</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4482,38 +4488,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563954</v>
+        <v>564058</v>
       </c>
       <c r="R36" t="n">
-        <v>6703267</v>
+        <v>6703198</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4572,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905253</v>
+        <v>121905245</v>
       </c>
       <c r="B37" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563982</v>
+        <v>563978</v>
       </c>
       <c r="R37" t="n">
-        <v>6703249</v>
+        <v>6703314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4674,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905268</v>
+        <v>121905260</v>
       </c>
       <c r="B38" t="n">
-        <v>5173</v>
+        <v>91194</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4686,43 +4700,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564170</v>
+        <v>563977</v>
       </c>
       <c r="R38" t="n">
-        <v>6703165</v>
+        <v>6703232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4781,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905270</v>
+        <v>121905244</v>
       </c>
       <c r="B39" t="n">
-        <v>91141</v>
+        <v>90754</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4793,25 +4802,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4821,10 +4830,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563981</v>
+        <v>563967</v>
       </c>
       <c r="R39" t="n">
-        <v>6703238</v>
+        <v>6703314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4857,11 +4866,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905261</v>
+        <v>121905254</v>
       </c>
       <c r="B40" t="n">
-        <v>91031</v>
+        <v>90754</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4904,21 +4908,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4928,10 +4932,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563990</v>
+        <v>564000</v>
       </c>
       <c r="R40" t="n">
-        <v>6703247</v>
+        <v>6703261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4990,10 +4994,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905252</v>
+        <v>121905268</v>
       </c>
       <c r="B41" t="n">
-        <v>90745</v>
+        <v>5173</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5002,38 +5006,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563976</v>
+        <v>564170</v>
       </c>
       <c r="R41" t="n">
-        <v>6703236</v>
+        <v>6703165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5092,10 +5101,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905251</v>
+        <v>121905270</v>
       </c>
       <c r="B42" t="n">
-        <v>90745</v>
+        <v>91150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5104,25 +5113,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5132,10 +5141,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563979</v>
+        <v>563981</v>
       </c>
       <c r="R42" t="n">
-        <v>6703240</v>
+        <v>6703238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5168,6 +5177,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5194,10 +5208,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905263</v>
+        <v>121905252</v>
       </c>
       <c r="B43" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5206,46 +5220,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564103</v>
+        <v>563976</v>
       </c>
       <c r="R43" t="n">
-        <v>6703266</v>
+        <v>6703236</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5280,18 +5286,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905263</v>
+        <v>121905270</v>
       </c>
       <c r="B29" t="n">
-        <v>98149</v>
+        <v>91157</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,46 +3760,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564103</v>
+        <v>563981</v>
       </c>
       <c r="R29" t="n">
-        <v>6703266</v>
+        <v>6703238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3836,7 +3828,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3845,7 +3837,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3864,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905247</v>
+        <v>121905268</v>
       </c>
       <c r="B30" t="n">
-        <v>90754</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,38 +3867,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563953</v>
+        <v>564170</v>
       </c>
       <c r="R30" t="n">
-        <v>6703296</v>
+        <v>6703165</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905250</v>
+        <v>121905249</v>
       </c>
       <c r="B31" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4006,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563964</v>
+        <v>563954</v>
       </c>
       <c r="R31" t="n">
-        <v>6703266</v>
+        <v>6703267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4068,10 +4064,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905261</v>
+        <v>121905253</v>
       </c>
       <c r="B32" t="n">
-        <v>91040</v>
+        <v>90761</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,21 +4080,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4104,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563990</v>
+        <v>563982</v>
       </c>
       <c r="R32" t="n">
-        <v>6703247</v>
+        <v>6703249</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4170,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905251</v>
+        <v>121905260</v>
       </c>
       <c r="B33" t="n">
-        <v>90754</v>
+        <v>91201</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4182,25 +4178,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4210,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563979</v>
+        <v>563977</v>
       </c>
       <c r="R33" t="n">
-        <v>6703240</v>
+        <v>6703232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4272,10 +4268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905253</v>
+        <v>121905247</v>
       </c>
       <c r="B34" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563982</v>
+        <v>563953</v>
       </c>
       <c r="R34" t="n">
-        <v>6703249</v>
+        <v>6703296</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4374,10 +4370,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905249</v>
+        <v>121905244</v>
       </c>
       <c r="B35" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,10 +4410,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563954</v>
+        <v>563967</v>
       </c>
       <c r="R35" t="n">
-        <v>6703267</v>
+        <v>6703314</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4476,10 +4472,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905256</v>
+        <v>121905245</v>
       </c>
       <c r="B36" t="n">
-        <v>56581</v>
+        <v>90761</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4488,46 +4484,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564058</v>
+        <v>563978</v>
       </c>
       <c r="R36" t="n">
-        <v>6703198</v>
+        <v>6703314</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,10 +4574,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905245</v>
+        <v>121905254</v>
       </c>
       <c r="B37" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,10 +4614,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563978</v>
+        <v>564000</v>
       </c>
       <c r="R37" t="n">
-        <v>6703314</v>
+        <v>6703261</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,10 +4676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905260</v>
+        <v>121905261</v>
       </c>
       <c r="B38" t="n">
-        <v>91194</v>
+        <v>91047</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4700,25 +4688,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4716,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563977</v>
+        <v>563990</v>
       </c>
       <c r="R38" t="n">
-        <v>6703232</v>
+        <v>6703247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4790,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905244</v>
+        <v>121905250</v>
       </c>
       <c r="B39" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4830,10 +4818,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563967</v>
+        <v>563964</v>
       </c>
       <c r="R39" t="n">
-        <v>6703314</v>
+        <v>6703266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4892,10 +4880,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905254</v>
+        <v>121905251</v>
       </c>
       <c r="B40" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4932,10 +4920,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564000</v>
+        <v>563979</v>
       </c>
       <c r="R40" t="n">
-        <v>6703261</v>
+        <v>6703240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4994,10 +4982,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905268</v>
+        <v>121905252</v>
       </c>
       <c r="B41" t="n">
-        <v>5173</v>
+        <v>90761</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5006,43 +4994,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564170</v>
+        <v>563976</v>
       </c>
       <c r="R41" t="n">
-        <v>6703165</v>
+        <v>6703236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5101,10 +5084,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905270</v>
+        <v>121905256</v>
       </c>
       <c r="B42" t="n">
-        <v>91150</v>
+        <v>56582</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5117,34 +5100,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563981</v>
+        <v>564058</v>
       </c>
       <c r="R42" t="n">
-        <v>6703238</v>
+        <v>6703198</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5177,11 +5168,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905252</v>
+        <v>121905263</v>
       </c>
       <c r="B43" t="n">
-        <v>90754</v>
+        <v>98157</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5220,38 +5206,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563976</v>
+        <v>564103</v>
       </c>
       <c r="R43" t="n">
-        <v>6703236</v>
+        <v>6703266</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5286,12 +5280,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3855,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905268</v>
+        <v>121905249</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>90761</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,43 +3867,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564170</v>
+        <v>563954</v>
       </c>
       <c r="R30" t="n">
-        <v>6703165</v>
+        <v>6703267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905249</v>
+        <v>121905268</v>
       </c>
       <c r="B31" t="n">
-        <v>90761</v>
+        <v>5173</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,38 +3969,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563954</v>
+        <v>564170</v>
       </c>
       <c r="R31" t="n">
-        <v>6703267</v>
+        <v>6703165</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905270</v>
+        <v>121905261</v>
       </c>
       <c r="B29" t="n">
-        <v>91157</v>
+        <v>91049</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,25 +3760,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563981</v>
+        <v>563990</v>
       </c>
       <c r="R29" t="n">
-        <v>6703238</v>
+        <v>6703247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3824,11 +3824,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3858,7 +3853,7 @@
         <v>121905249</v>
       </c>
       <c r="B30" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3957,10 +3952,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905268</v>
+        <v>121905253</v>
       </c>
       <c r="B31" t="n">
-        <v>5173</v>
+        <v>90763</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,43 +3964,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564170</v>
+        <v>563982</v>
       </c>
       <c r="R31" t="n">
-        <v>6703165</v>
+        <v>6703249</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4064,10 +4054,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905253</v>
+        <v>121905252</v>
       </c>
       <c r="B32" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4104,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563982</v>
+        <v>563976</v>
       </c>
       <c r="R32" t="n">
-        <v>6703249</v>
+        <v>6703236</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4166,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905260</v>
+        <v>121905244</v>
       </c>
       <c r="B33" t="n">
-        <v>91201</v>
+        <v>90763</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,25 +4168,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563977</v>
+        <v>563967</v>
       </c>
       <c r="R33" t="n">
-        <v>6703232</v>
+        <v>6703314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,10 +4258,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905247</v>
+        <v>121905254</v>
       </c>
       <c r="B34" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4308,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563953</v>
+        <v>564000</v>
       </c>
       <c r="R34" t="n">
-        <v>6703296</v>
+        <v>6703261</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4370,10 +4360,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905244</v>
+        <v>121905268</v>
       </c>
       <c r="B35" t="n">
-        <v>90761</v>
+        <v>5173</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,38 +4372,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563967</v>
+        <v>564170</v>
       </c>
       <c r="R35" t="n">
-        <v>6703314</v>
+        <v>6703165</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4472,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905245</v>
+        <v>121905251</v>
       </c>
       <c r="B36" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4512,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563978</v>
+        <v>563979</v>
       </c>
       <c r="R36" t="n">
-        <v>6703314</v>
+        <v>6703240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4574,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905254</v>
+        <v>121905250</v>
       </c>
       <c r="B37" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4614,10 +4609,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564000</v>
+        <v>563964</v>
       </c>
       <c r="R37" t="n">
-        <v>6703261</v>
+        <v>6703266</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4676,10 +4671,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905261</v>
+        <v>121905263</v>
       </c>
       <c r="B38" t="n">
-        <v>91047</v>
+        <v>98159</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4688,38 +4683,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563990</v>
+        <v>564103</v>
       </c>
       <c r="R38" t="n">
-        <v>6703247</v>
+        <v>6703266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4754,12 +4757,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4778,10 +4787,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905250</v>
+        <v>121905256</v>
       </c>
       <c r="B39" t="n">
-        <v>90761</v>
+        <v>56584</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,38 +4799,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563964</v>
+        <v>564058</v>
       </c>
       <c r="R39" t="n">
-        <v>6703266</v>
+        <v>6703198</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4880,10 +4897,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905251</v>
+        <v>121905245</v>
       </c>
       <c r="B40" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4920,10 +4937,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563979</v>
+        <v>563978</v>
       </c>
       <c r="R40" t="n">
-        <v>6703240</v>
+        <v>6703314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905252</v>
+        <v>121905270</v>
       </c>
       <c r="B41" t="n">
-        <v>90761</v>
+        <v>91159</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4994,25 +5011,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5022,10 +5039,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563976</v>
+        <v>563981</v>
       </c>
       <c r="R41" t="n">
-        <v>6703236</v>
+        <v>6703238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5058,6 +5075,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,10 +5106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905256</v>
+        <v>121905247</v>
       </c>
       <c r="B42" t="n">
-        <v>56582</v>
+        <v>90763</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,46 +5118,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564058</v>
+        <v>563953</v>
       </c>
       <c r="R42" t="n">
-        <v>6703198</v>
+        <v>6703296</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5194,10 +5208,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905263</v>
+        <v>121905260</v>
       </c>
       <c r="B43" t="n">
-        <v>98157</v>
+        <v>91203</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5210,42 +5224,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564103</v>
+        <v>563977</v>
       </c>
       <c r="R43" t="n">
-        <v>6703266</v>
+        <v>6703232</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5280,18 +5286,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905261</v>
+        <v>121905252</v>
       </c>
       <c r="B29" t="n">
-        <v>91049</v>
+        <v>90763</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563990</v>
+        <v>563976</v>
       </c>
       <c r="R29" t="n">
-        <v>6703247</v>
+        <v>6703236</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905249</v>
+        <v>121905247</v>
       </c>
       <c r="B30" t="n">
         <v>90763</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563954</v>
+        <v>563953</v>
       </c>
       <c r="R30" t="n">
-        <v>6703267</v>
+        <v>6703296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3952,10 +3952,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905253</v>
+        <v>121905270</v>
       </c>
       <c r="B31" t="n">
-        <v>90763</v>
+        <v>91159</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,25 +3964,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563982</v>
+        <v>563981</v>
       </c>
       <c r="R31" t="n">
-        <v>6703249</v>
+        <v>6703238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,6 +4028,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4054,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905252</v>
+        <v>121905244</v>
       </c>
       <c r="B32" t="n">
         <v>90763</v>
@@ -4094,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563976</v>
+        <v>563967</v>
       </c>
       <c r="R32" t="n">
-        <v>6703236</v>
+        <v>6703314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,10 +4161,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905244</v>
+        <v>121905256</v>
       </c>
       <c r="B33" t="n">
-        <v>90763</v>
+        <v>56584</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,38 +4173,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563967</v>
+        <v>564058</v>
       </c>
       <c r="R33" t="n">
-        <v>6703314</v>
+        <v>6703198</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4258,7 +4271,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905254</v>
+        <v>121905253</v>
       </c>
       <c r="B34" t="n">
         <v>90763</v>
@@ -4298,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564000</v>
+        <v>563982</v>
       </c>
       <c r="R34" t="n">
-        <v>6703261</v>
+        <v>6703249</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4360,10 +4373,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905268</v>
+        <v>121905254</v>
       </c>
       <c r="B35" t="n">
-        <v>5173</v>
+        <v>90763</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4372,43 +4385,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564170</v>
+        <v>564000</v>
       </c>
       <c r="R35" t="n">
-        <v>6703165</v>
+        <v>6703261</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905251</v>
+        <v>121905245</v>
       </c>
       <c r="B36" t="n">
         <v>90763</v>
@@ -4507,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563979</v>
+        <v>563978</v>
       </c>
       <c r="R36" t="n">
-        <v>6703240</v>
+        <v>6703314</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,10 +4577,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905250</v>
+        <v>121905261</v>
       </c>
       <c r="B37" t="n">
-        <v>90763</v>
+        <v>91049</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4585,21 +4593,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4609,10 +4617,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563964</v>
+        <v>563990</v>
       </c>
       <c r="R37" t="n">
-        <v>6703266</v>
+        <v>6703247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4671,10 +4679,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905263</v>
+        <v>121905250</v>
       </c>
       <c r="B38" t="n">
-        <v>98159</v>
+        <v>90763</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4683,43 +4691,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564103</v>
+        <v>563964</v>
       </c>
       <c r="R38" t="n">
         <v>6703266</v>
@@ -4757,18 +4757,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4787,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905256</v>
+        <v>121905263</v>
       </c>
       <c r="B39" t="n">
-        <v>56584</v>
+        <v>98159</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4799,35 +4793,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4835,10 +4829,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564058</v>
+        <v>564103</v>
       </c>
       <c r="R39" t="n">
-        <v>6703198</v>
+        <v>6703266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,12 +4867,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905245</v>
+        <v>121905268</v>
       </c>
       <c r="B40" t="n">
-        <v>90763</v>
+        <v>5173</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4909,38 +4909,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563978</v>
+        <v>564170</v>
       </c>
       <c r="R40" t="n">
-        <v>6703314</v>
+        <v>6703165</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4999,10 +5004,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905270</v>
+        <v>121905249</v>
       </c>
       <c r="B41" t="n">
-        <v>91159</v>
+        <v>90763</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5011,25 +5016,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5039,10 +5044,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563981</v>
+        <v>563954</v>
       </c>
       <c r="R41" t="n">
-        <v>6703238</v>
+        <v>6703267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5075,11 +5080,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,10 +5106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905247</v>
+        <v>121905260</v>
       </c>
       <c r="B42" t="n">
-        <v>90763</v>
+        <v>91203</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5118,25 +5118,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563953</v>
+        <v>563977</v>
       </c>
       <c r="R42" t="n">
-        <v>6703296</v>
+        <v>6703232</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905260</v>
+        <v>121905251</v>
       </c>
       <c r="B43" t="n">
-        <v>91203</v>
+        <v>90763</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5220,25 +5220,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563977</v>
+        <v>563979</v>
       </c>
       <c r="R43" t="n">
-        <v>6703232</v>
+        <v>6703240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905263</v>
+        <v>121905261</v>
       </c>
       <c r="B29" t="n">
-        <v>98175</v>
+        <v>91065</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,46 +3760,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564103</v>
+        <v>563990</v>
       </c>
       <c r="R29" t="n">
-        <v>6703266</v>
+        <v>6703247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,18 +3826,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3864,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905260</v>
+        <v>121905268</v>
       </c>
       <c r="B30" t="n">
-        <v>91219</v>
+        <v>5173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,38 +3862,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563977</v>
+        <v>564170</v>
       </c>
       <c r="R30" t="n">
-        <v>6703232</v>
+        <v>6703165</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,10 +3957,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905256</v>
+        <v>121905270</v>
       </c>
       <c r="B31" t="n">
-        <v>56584</v>
+        <v>91175</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,42 +3973,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564058</v>
+        <v>563981</v>
       </c>
       <c r="R31" t="n">
-        <v>6703198</v>
+        <v>6703238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4050,6 +4033,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,10 +4064,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905268</v>
+        <v>121905260</v>
       </c>
       <c r="B32" t="n">
-        <v>5173</v>
+        <v>91219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,43 +4076,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564170</v>
+        <v>563977</v>
       </c>
       <c r="R32" t="n">
-        <v>6703165</v>
+        <v>6703232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905270</v>
+        <v>121905249</v>
       </c>
       <c r="B33" t="n">
-        <v>91175</v>
+        <v>90779</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,25 +4178,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4223,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563981</v>
+        <v>563954</v>
       </c>
       <c r="R33" t="n">
-        <v>6703238</v>
+        <v>6703267</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,11 +4242,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4290,7 +4268,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905245</v>
+        <v>121905253</v>
       </c>
       <c r="B34" t="n">
         <v>90779</v>
@@ -4330,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563978</v>
+        <v>563982</v>
       </c>
       <c r="R34" t="n">
-        <v>6703314</v>
+        <v>6703249</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4392,7 +4370,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905252</v>
+        <v>121905244</v>
       </c>
       <c r="B35" t="n">
         <v>90779</v>
@@ -4432,10 +4410,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563976</v>
+        <v>563967</v>
       </c>
       <c r="R35" t="n">
-        <v>6703236</v>
+        <v>6703314</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4494,10 +4472,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905253</v>
+        <v>121905263</v>
       </c>
       <c r="B36" t="n">
-        <v>90779</v>
+        <v>98175</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,38 +4484,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563982</v>
+        <v>564103</v>
       </c>
       <c r="R36" t="n">
-        <v>6703249</v>
+        <v>6703266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4572,12 +4558,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4596,7 +4588,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905254</v>
+        <v>121905247</v>
       </c>
       <c r="B37" t="n">
         <v>90779</v>
@@ -4636,10 +4628,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564000</v>
+        <v>563953</v>
       </c>
       <c r="R37" t="n">
-        <v>6703261</v>
+        <v>6703296</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,7 +4690,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905251</v>
+        <v>121905245</v>
       </c>
       <c r="B38" t="n">
         <v>90779</v>
@@ -4738,10 +4730,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563979</v>
+        <v>563978</v>
       </c>
       <c r="R38" t="n">
-        <v>6703240</v>
+        <v>6703314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4800,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905247</v>
+        <v>121905256</v>
       </c>
       <c r="B39" t="n">
-        <v>90779</v>
+        <v>56584</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4812,38 +4804,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563953</v>
+        <v>564058</v>
       </c>
       <c r="R39" t="n">
-        <v>6703296</v>
+        <v>6703198</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905244</v>
+        <v>121905251</v>
       </c>
       <c r="B40" t="n">
         <v>90779</v>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563967</v>
+        <v>563979</v>
       </c>
       <c r="R40" t="n">
-        <v>6703314</v>
+        <v>6703240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905250</v>
+        <v>121905252</v>
       </c>
       <c r="B41" t="n">
         <v>90779</v>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563964</v>
+        <v>563976</v>
       </c>
       <c r="R41" t="n">
-        <v>6703266</v>
+        <v>6703236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905261</v>
+        <v>121905254</v>
       </c>
       <c r="B42" t="n">
-        <v>91065</v>
+        <v>90779</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5122,21 +5122,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563990</v>
+        <v>564000</v>
       </c>
       <c r="R42" t="n">
-        <v>6703247</v>
+        <v>6703261</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905249</v>
+        <v>121905250</v>
       </c>
       <c r="B43" t="n">
         <v>90779</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563954</v>
+        <v>563964</v>
       </c>
       <c r="R43" t="n">
-        <v>6703267</v>
+        <v>6703266</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3957,10 +3957,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905270</v>
+        <v>121905260</v>
       </c>
       <c r="B31" t="n">
-        <v>91175</v>
+        <v>91219</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,25 +3969,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4217</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563981</v>
+        <v>563977</v>
       </c>
       <c r="R31" t="n">
-        <v>6703238</v>
+        <v>6703232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4033,11 +4033,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,10 +4059,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905260</v>
+        <v>121905270</v>
       </c>
       <c r="B32" t="n">
-        <v>91219</v>
+        <v>91175</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,25 +4071,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4104,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563977</v>
+        <v>563981</v>
       </c>
       <c r="R32" t="n">
-        <v>6703232</v>
+        <v>6703238</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,6 +4135,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 58943-2023 artfynd.xlsx
+++ b/artfynd/A 58943-2023 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121905261</v>
+        <v>121905249</v>
       </c>
       <c r="B29" t="n">
-        <v>91065</v>
+        <v>90789</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563990</v>
+        <v>563954</v>
       </c>
       <c r="R29" t="n">
-        <v>6703247</v>
+        <v>6703267</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121905268</v>
+        <v>121905244</v>
       </c>
       <c r="B30" t="n">
-        <v>5173</v>
+        <v>90789</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,43 +3862,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564170</v>
+        <v>563967</v>
       </c>
       <c r="R30" t="n">
-        <v>6703165</v>
+        <v>6703314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3957,10 +3952,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121905260</v>
+        <v>121905263</v>
       </c>
       <c r="B31" t="n">
-        <v>91219</v>
+        <v>98185</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,34 +3968,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563977</v>
+        <v>564103</v>
       </c>
       <c r="R31" t="n">
-        <v>6703232</v>
+        <v>6703266</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,12 +4038,18 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4059,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121905270</v>
+        <v>121905256</v>
       </c>
       <c r="B32" t="n">
-        <v>91175</v>
+        <v>56584</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4075,34 +4084,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563981</v>
+        <v>564058</v>
       </c>
       <c r="R32" t="n">
-        <v>6703238</v>
+        <v>6703198</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4135,11 +4152,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4166,10 +4178,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121905249</v>
+        <v>121905268</v>
       </c>
       <c r="B33" t="n">
-        <v>90779</v>
+        <v>5173</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,38 +4190,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563954</v>
+        <v>564170</v>
       </c>
       <c r="R33" t="n">
-        <v>6703267</v>
+        <v>6703165</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,10 +4285,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121905253</v>
+        <v>121905261</v>
       </c>
       <c r="B34" t="n">
-        <v>90779</v>
+        <v>91075</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,21 +4301,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4308,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563982</v>
+        <v>563990</v>
       </c>
       <c r="R34" t="n">
-        <v>6703249</v>
+        <v>6703247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4370,10 +4387,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121905244</v>
+        <v>121905245</v>
       </c>
       <c r="B35" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,7 +4427,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563967</v>
+        <v>563978</v>
       </c>
       <c r="R35" t="n">
         <v>6703314</v>
@@ -4472,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121905263</v>
+        <v>121905250</v>
       </c>
       <c r="B36" t="n">
-        <v>98175</v>
+        <v>90789</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4484,43 +4501,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564103</v>
+        <v>563964</v>
       </c>
       <c r="R36" t="n">
         <v>6703266</v>
@@ -4558,18 +4567,12 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4588,10 +4591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121905247</v>
+        <v>121905254</v>
       </c>
       <c r="B37" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4628,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563953</v>
+        <v>564000</v>
       </c>
       <c r="R37" t="n">
-        <v>6703296</v>
+        <v>6703261</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4690,10 +4693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121905245</v>
+        <v>121905252</v>
       </c>
       <c r="B38" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4730,10 +4733,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563978</v>
+        <v>563976</v>
       </c>
       <c r="R38" t="n">
-        <v>6703314</v>
+        <v>6703236</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,10 +4795,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121905256</v>
+        <v>121905253</v>
       </c>
       <c r="B39" t="n">
-        <v>56584</v>
+        <v>90789</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4804,46 +4807,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564058</v>
+        <v>563982</v>
       </c>
       <c r="R39" t="n">
-        <v>6703198</v>
+        <v>6703249</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4902,10 +4897,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121905251</v>
+        <v>121905270</v>
       </c>
       <c r="B40" t="n">
-        <v>90779</v>
+        <v>91185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4914,25 +4909,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4942,10 +4937,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563979</v>
+        <v>563981</v>
       </c>
       <c r="R40" t="n">
-        <v>6703240</v>
+        <v>6703238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,6 +4973,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5004,10 +5004,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121905252</v>
+        <v>121905260</v>
       </c>
       <c r="B41" t="n">
-        <v>90779</v>
+        <v>91229</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,25 +5016,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563976</v>
+        <v>563977</v>
       </c>
       <c r="R41" t="n">
-        <v>6703236</v>
+        <v>6703232</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121905254</v>
+        <v>121905251</v>
       </c>
       <c r="B42" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564000</v>
+        <v>563979</v>
       </c>
       <c r="R42" t="n">
-        <v>6703261</v>
+        <v>6703240</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121905250</v>
+        <v>121905247</v>
       </c>
       <c r="B43" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563964</v>
+        <v>563953</v>
       </c>
       <c r="R43" t="n">
-        <v>6703266</v>
+        <v>6703296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
